--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -1,103 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SelectorPredicate" sheetId="1" r:id="rId1"/>
+    <sheet name="SelectorPredicate" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>SelectorPredicate</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>2ef941ecf75f8eed</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>selector_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>predicate</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;Selector.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>union&lt;SelectorPredicateNode&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -410,106 +407,179 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SelectorPredicate</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2ef941ecf75f8eed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>selector_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>predicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>selector_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>predicate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;Selector.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>union&lt;SelectorPredicateNode&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>24252</v>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>21</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":31}</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,6 +582,71 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980409</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980407</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":13,"maximum_index":14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>980406</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":980401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>980407</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":980401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>980409</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":980401}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,6 +647,32 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>990407</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":990406}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>990405</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":990501}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,6 +673,19 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1000407</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":990503}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,305 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1020415</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1020414}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1020416</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1020414}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1020413</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1020418}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1020420</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1020418}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1020413</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1020420</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020412</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1020418</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1020419</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1020414</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1020419</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1020420</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1020409</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1020508}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1020410</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1020412</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1020413</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1020414</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1020415</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1020416</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1020418</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1020419</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1020420</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1020411</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020402}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -985,6 +985,97 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1030408</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1030405}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1030411</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1030405}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1030412</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1030410}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1030409</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1030410</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1030411</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1030413</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1030401}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,6 +1076,32 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1040409</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1040404}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1040408</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1040401}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,6 +1102,19 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1050405</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1050501}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,6 +1115,383 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1060410</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1060420</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1060430</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1060411</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1060421</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1060431</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1060442</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1060452</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1060443</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":11,"maximum_index":11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1060453</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":11,"maximum_index":11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1060412</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1060422</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1060432</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1060413</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1060423</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1060433</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1060440</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":8,"maximum_index":8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1060450</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":8,"maximum_index":8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1060441</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":9,"maximum_index":9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1060451</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":9,"maximum_index":9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1060407</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1060505}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1060440</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1060441</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1060442</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1060443</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1060450</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1060451</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1060452</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1060453</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1492,6 +1492,97 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1070411</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1070402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1070404</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1070403}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1070409</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1070403}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1070408</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1070409</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1070410</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1070407</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1070503}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1583,6 +1583,32 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1080407</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1080503}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1080408</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1080401}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,6 +582,1033 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980409</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980407</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":13,"maximum_index":14}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>980406</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":980401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>980407</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":980401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>980409</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":980401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>990407</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":990406}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>990405</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":990501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1000407</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":990503}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1020415</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1020414}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1020416</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1020414}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1020413</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1020418}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1020420</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1020418}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1020413</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1020420</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":5}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1020412</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1020418</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1020419</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1020414</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1020419</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1020420</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1020409</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1020508}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1020410</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1020412</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1020413</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1020414</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1020415</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1020416</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1020418</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1020419</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1020420</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1020411</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1020402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1030408</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1030405}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1030411</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1030405}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1030412</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1030410}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1030409</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1030410</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1030411</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1030413</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1030401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1040409</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1040404}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1040408</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1040401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1050405</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1050501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1060410</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1060420</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1060430</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>1060411</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>1060421</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>1060431</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="n">
+        <v>1060442</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="n">
+        <v>1060452</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":10}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="n">
+        <v>1060443</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":11,"maximum_index":11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="n">
+        <v>1060453</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":11,"maximum_index":11}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="n">
+        <v>1060412</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="n">
+        <v>1060422</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="n">
+        <v>1060432</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="n">
+        <v>1060413</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="n">
+        <v>1060423</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="n">
+        <v>1060433</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n">
+        <v>1060440</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":8,"maximum_index":8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="n">
+        <v>1060450</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":8,"maximum_index":8}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="n">
+        <v>1060441</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":9,"maximum_index":9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="n">
+        <v>1060451</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{"type":"FormationRange","minimum_index":9,"maximum_index":9}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="n">
+        <v>1060407</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1060505}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="n">
+        <v>1060440</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="n">
+        <v>1060441</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="n">
+        <v>1060442</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="n">
+        <v>1060443</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="n">
+        <v>1060450</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="n">
+        <v>1060451</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="n">
+        <v>1060452</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="n">
+        <v>1060453</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="n">
+        <v>1070411</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1070402}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="n">
+        <v>1070404</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1070403}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="n">
+        <v>1070409</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{"type":"Excludes","excluded_selector_id":1070403}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="n">
+        <v>1070408</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="n">
+        <v>1070409</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="n">
+        <v>1070410</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="n">
+        <v>1070407</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1070503}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="n">
+        <v>1080407</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{"type":"HasEffect","effect_id":1080503}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="n">
+        <v>1080408</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{"type":"OwnedBy","owner_selector_id":1080401}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/SelectorPredicate.xlsx
+++ b/config/data/SelectorPredicate.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SelectorPredicate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SelectorPredicate" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,167 +499,183 @@
   </sheetPr>
   <dimension ref="A1:J87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="16.7109375" customWidth="1" style="5" min="2" max="2"/>
+    <col width="12.7109375" customWidth="1" style="5" min="3" max="3"/>
+    <col width="28.7109375" customWidth="1" style="5" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>SelectorPredicate</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>2ef941ecf75f8eed</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>b6552ecb9d4f5a2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>selector_id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>sequence</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>selector_id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>sequence</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>predicate</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>ref&lt;Selector.id&gt;</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>i32</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>union&lt;SelectorPredicateNode&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>range=1..100</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="D6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>24252</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24252</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -583,11 +684,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>980409</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>980409</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -596,11 +701,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>980407</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>980407</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -609,11 +718,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>980406</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>980406</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -622,11 +735,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>980407</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>980407</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -635,11 +752,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>980409</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>980409</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -648,11 +769,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>990407</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>990407</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -661,11 +786,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>990405</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>990405</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -674,11 +803,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>1000407</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1000407</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -687,929 +820,1099 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>1020415</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1040409</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1020414}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1040404}</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>1020416</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1040408</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1020414}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1040401}</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>1020413</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1050405</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1020418}</t>
+          <t>{"type":"HasEffect","effect_id":1050501}</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>1020420</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1060410</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1020418}</t>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>1020413</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1060420</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":5}</t>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>1020420</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1060430</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":5}</t>
+          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>1020412</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1060411</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>1020418</v>
-      </c>
-      <c r="C24" t="n">
-        <v>2</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1060421</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>1020419</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1060431</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>1020414</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1060442</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1020506}</t>
+          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":10}</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>1020419</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1060452</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1020506}</t>
+          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":10}</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>1020420</v>
-      </c>
-      <c r="C28" t="n">
-        <v>4</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1060443</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1020506}</t>
+          <t>{"type":"FormationRange","minimum_index":11,"maximum_index":11}</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>1020409</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1060453</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1020508}</t>
+          <t>{"type":"FormationRange","minimum_index":11,"maximum_index":11}</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>1020410</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1060412</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>1020412</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1060422</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
-        <v>1020413</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1060432</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
-        <v>1020414</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1060413</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>1020415</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1060423</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>1020416</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1060433</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>1020418</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1060440</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":8,"maximum_index":8}</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
-        <v>1020419</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1060450</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":8,"maximum_index":8}</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
-        <v>1020420</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1060441</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
+          <t>{"type":"FormationRange","minimum_index":9,"maximum_index":9}</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
-        <v>1020411</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1060451</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1020402}</t>
+          <t>{"type":"FormationRange","minimum_index":9,"maximum_index":9}</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
-        <v>1030408</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1060407</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1030405}</t>
+          <t>{"type":"HasEffect","effect_id":1060505}</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
-        <v>1030411</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1060440</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1030405}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
-        <v>1030412</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1060441</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1030410}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>1030409</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1060442</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1030501}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
-        <v>1030410</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1060443</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1030501}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>1030411</v>
-      </c>
-      <c r="C45" t="n">
-        <v>2</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1060450</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1030501}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
-        <v>1030413</v>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1060451</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1030401}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
-        <v>1040409</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1060452</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1040404}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="n">
-        <v>1040408</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1060453</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1040401}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="n">
-        <v>1050405</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1070411</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1050501}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1070402}</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="n">
-        <v>1060410</v>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1070404</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1070403}</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="n">
-        <v>1060420</v>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1070409</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1070403}</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="n">
-        <v>1060430</v>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1070408</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":0,"maximum_index":0}</t>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="n">
-        <v>1060411</v>
-      </c>
-      <c r="C53" t="n">
-        <v>1</v>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1070409</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="n">
-        <v>1060421</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1070410</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+          <t>{"type":"HasEffect","effect_id":1070501}</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="n">
-        <v>1060431</v>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1070407</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":1}</t>
+          <t>{"type":"HasEffect","effect_id":1070503}</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="n">
-        <v>1060442</v>
-      </c>
-      <c r="C56" t="n">
-        <v>2</v>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1080407</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":10}</t>
+          <t>{"type":"HasEffect","effect_id":1080503}</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="n">
-        <v>1060452</v>
-      </c>
-      <c r="C57" t="n">
-        <v>2</v>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1080408</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":10,"maximum_index":10}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1080401}</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="n">
-        <v>1060443</v>
+        <v>1020415</v>
       </c>
       <c r="C58" t="n">
         <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":11,"maximum_index":11}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1020414}</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>1060453</v>
+        <v>1020416</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":11,"maximum_index":11}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1020414}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>1060412</v>
+        <v>1020413</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1020418}</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>1060422</v>
+        <v>1020420</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1020418}</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="n">
-        <v>1060432</v>
+        <v>1020413</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":2}</t>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":5}</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" t="n">
-        <v>1060413</v>
+        <v>1020420</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+          <t>{"type":"FormationRange","minimum_index":1,"maximum_index":5}</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" t="n">
-        <v>1060423</v>
+        <v>1020412</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="n">
-        <v>1060433</v>
+        <v>1020418</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":3,"maximum_index":3}</t>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" t="n">
-        <v>1060440</v>
+        <v>1020419</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":8,"maximum_index":8}</t>
+          <t>{"type":"FormationRange","minimum_index":2,"maximum_index":4}</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" t="n">
-        <v>1060450</v>
+        <v>1020414</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":8,"maximum_index":8}</t>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" t="n">
-        <v>1060441</v>
+        <v>1020419</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":9,"maximum_index":9}</t>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" t="n">
-        <v>1060451</v>
+        <v>1020420</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{"type":"FormationRange","minimum_index":9,"maximum_index":9}</t>
+          <t>{"type":"HasEffect","effect_id":1020506}</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" t="n">
-        <v>1060407</v>
+        <v>1020409</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1060505}</t>
+          <t>{"type":"HasEffect","effect_id":1020508}</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="n">
-        <v>1060440</v>
+        <v>1020410</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="n">
-        <v>1060441</v>
+        <v>1020412</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="n">
-        <v>1060442</v>
+        <v>1020413</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="n">
-        <v>1060443</v>
+        <v>1020414</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1060401}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="n">
-        <v>1060450</v>
+        <v>1020415</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="n">
-        <v>1060451</v>
+        <v>1020416</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="n">
-        <v>1060452</v>
+        <v>1020418</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="n">
-        <v>1060453</v>
+        <v>1020419</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1060402}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" t="n">
-        <v>1070411</v>
+        <v>1020420</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1070402}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020401}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="n">
-        <v>1070404</v>
+        <v>1020411</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1070403}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1020402}</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" t="n">
-        <v>1070409</v>
+        <v>1030408</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{"type":"Excludes","excluded_selector_id":1070403}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1030405}</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" t="n">
-        <v>1070408</v>
+        <v>1030411</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1070501}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1030405}</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" t="n">
-        <v>1070409</v>
+        <v>1030412</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1070501}</t>
+          <t>{"type":"Excludes","excluded_selector_id":1030410}</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" t="n">
-        <v>1070410</v>
+        <v>1030409</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1070501}</t>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" t="n">
-        <v>1070407</v>
+        <v>1030410</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1070503}</t>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" t="n">
-        <v>1080407</v>
+        <v>1030411</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{"type":"HasEffect","effect_id":1080503}</t>
+          <t>{"type":"HasEffect","effect_id":1030501}</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" t="n">
-        <v>1080408</v>
+        <v>1030413</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{"type":"OwnedBy","owner_selector_id":1080401}</t>
+          <t>{"type":"OwnedBy","owner_selector_id":1030403}</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C8:C1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." type="whole">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>